--- a/artfynd/A 64125-2021 artfynd.xlsx
+++ b/artfynd/A 64125-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64125-2021 artfynd.xlsx
+++ b/artfynd/A 64125-2021 artfynd.xlsx
@@ -2959,7 +2959,7 @@
         <v>112795542</v>
       </c>
       <c r="B23" t="n">
-        <v>5161</v>
+        <v>5166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 64125-2021 artfynd.xlsx
+++ b/artfynd/A 64125-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112795459</v>
+        <v>112795483</v>
       </c>
       <c r="B2" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475446</v>
+        <v>475420</v>
       </c>
       <c r="R2" t="n">
-        <v>6580219</v>
+        <v>6580113</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112795536</v>
+        <v>112795521</v>
       </c>
       <c r="B3" t="n">
-        <v>93865</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475311</v>
+        <v>475289</v>
       </c>
       <c r="R3" t="n">
-        <v>6579918</v>
+        <v>6579919</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,6 +862,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>gran högstubbe</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -892,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112795537</v>
+        <v>112795522</v>
       </c>
       <c r="B4" t="n">
-        <v>93865</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475364</v>
+        <v>475361</v>
       </c>
       <c r="R4" t="n">
-        <v>6579938</v>
+        <v>6580052</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,6 +968,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>rönnved</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -998,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112795538</v>
+        <v>112795511</v>
       </c>
       <c r="B5" t="n">
-        <v>93865</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>496</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Nordisk klipptuss</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cynodontium suecicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Arnell &amp; C.E.O.Jensen) I.Hagen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475407</v>
+        <v>475439</v>
       </c>
       <c r="R5" t="n">
-        <v>6580114</v>
+        <v>6580094</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1104,37 +1094,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112795511</v>
+        <v>112795506</v>
       </c>
       <c r="B6" t="n">
-        <v>93986</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>496</v>
+        <v>1102</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordisk klipptuss</t>
+          <t>Gäckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cynodontium suecicum</t>
+          <t>Postia parva</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Arnell &amp; C.E.O.Jenssen) I.Hagen</t>
+          <t>(Renvall) Renvall</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475439</v>
+        <v>475470</v>
       </c>
       <c r="R6" t="n">
-        <v>6580095</v>
+        <v>6580041</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1210,37 +1195,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112795476</v>
+        <v>112795471</v>
       </c>
       <c r="B7" t="n">
-        <v>93737</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2819</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475465</v>
+        <v>475392</v>
       </c>
       <c r="R7" t="n">
-        <v>6580213</v>
+        <v>6580025</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1296,6 +1276,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1316,15 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112795506</v>
+        <v>112795474</v>
       </c>
       <c r="B8" t="n">
-        <v>90140</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1102</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gäckporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Postia parva</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall) Renvall</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475471</v>
+        <v>475173</v>
       </c>
       <c r="R8" t="n">
-        <v>6580041</v>
+        <v>6579873</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1402,6 +1382,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,37 +1407,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112795458</v>
+        <v>112795475</v>
       </c>
       <c r="B9" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475361</v>
+        <v>475165</v>
       </c>
       <c r="R9" t="n">
-        <v>6580054</v>
+        <v>6579830</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1533,15 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112795491</v>
+        <v>112795536</v>
       </c>
       <c r="B10" t="n">
-        <v>83652</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,21 +1524,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3518</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1548,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475435</v>
+        <v>475311</v>
       </c>
       <c r="R10" t="n">
-        <v>6580103</v>
+        <v>6579918</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1639,15 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112795469</v>
+        <v>112795537</v>
       </c>
       <c r="B11" t="n">
-        <v>89902</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475188</v>
+        <v>475363</v>
       </c>
       <c r="R11" t="n">
-        <v>6579870</v>
+        <v>6579938</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1725,11 +1695,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1750,15 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112795522</v>
+        <v>112795538</v>
       </c>
       <c r="B12" t="n">
-        <v>74189</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>306</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475361</v>
+        <v>475407</v>
       </c>
       <c r="R12" t="n">
-        <v>6580052</v>
+        <v>6580114</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,11 +1796,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>rönnved</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1861,37 +1816,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112795516</v>
+        <v>112795488</v>
       </c>
       <c r="B13" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475497</v>
+        <v>475552</v>
       </c>
       <c r="R13" t="n">
-        <v>6580085</v>
+        <v>6580250</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1947,6 +1897,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>klippa</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1967,15 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112795523</v>
+        <v>112795476</v>
       </c>
       <c r="B14" t="n">
-        <v>91195</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,21 +1933,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4363</v>
+        <v>2819</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>475265</v>
+        <v>475465</v>
       </c>
       <c r="R14" t="n">
-        <v>6579997</v>
+        <v>6580213</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,37 +2023,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112795483</v>
+        <v>112795478</v>
       </c>
       <c r="B15" t="n">
-        <v>94733</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>291</v>
+        <v>2819</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>475420</v>
+        <v>475557</v>
       </c>
       <c r="R15" t="n">
-        <v>6580113</v>
+        <v>6580258</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2162,7 +2107,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>klippa</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2184,37 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112795471</v>
+        <v>112795491</v>
       </c>
       <c r="B16" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>3518</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>475391</v>
+        <v>475435</v>
       </c>
       <c r="R16" t="n">
-        <v>6580025</v>
+        <v>6580104</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2270,11 +2210,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2295,15 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112795521</v>
+        <v>112795523</v>
       </c>
       <c r="B17" t="n">
-        <v>74189</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>306</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475289</v>
+        <v>475265</v>
       </c>
       <c r="R17" t="n">
-        <v>6579919</v>
+        <v>6579998</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2381,11 +2311,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>gran högstubbe</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2406,15 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112795527</v>
+        <v>112795458</v>
       </c>
       <c r="B18" t="n">
-        <v>74187</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,21 +2342,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2446,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>475360</v>
+        <v>475361</v>
       </c>
       <c r="R18" t="n">
-        <v>6580059</v>
+        <v>6580054</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2495,7 +2415,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>asphögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2517,15 +2437,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112795528</v>
+        <v>112795459</v>
       </c>
       <c r="B19" t="n">
-        <v>74187</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>475386</v>
+        <v>475446</v>
       </c>
       <c r="R19" t="n">
-        <v>6580053</v>
+        <v>6580219</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2606,7 +2521,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>rönnved</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2628,37 +2543,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112795475</v>
+        <v>112795469</v>
       </c>
       <c r="B20" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2578,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>475165</v>
+        <v>475187</v>
       </c>
       <c r="R20" t="n">
-        <v>6579829</v>
+        <v>6579871</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2739,15 +2649,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112795514</v>
+        <v>112795481</v>
       </c>
       <c r="B21" t="n">
-        <v>91222</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,21 +2660,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2684,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>475267</v>
+        <v>475240</v>
       </c>
       <c r="R21" t="n">
-        <v>6579921</v>
+        <v>6580032</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2845,37 +2750,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112795497</v>
+        <v>112795513</v>
       </c>
       <c r="B22" t="n">
-        <v>74014</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>5966</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2885,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>475370</v>
+        <v>475251</v>
       </c>
       <c r="R22" t="n">
-        <v>6580036</v>
+        <v>6580043</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2931,11 +2831,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>björk</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2956,37 +2851,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112795542</v>
+        <v>112795514</v>
       </c>
       <c r="B23" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>475286</v>
+        <v>475267</v>
       </c>
       <c r="R23" t="n">
-        <v>6579916</v>
+        <v>6579922</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3055,6 +2945,526 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112795516</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>475497</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6580085</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112795497</v>
+      </c>
+      <c r="B25" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>475370</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6580036</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>björk</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>112795527</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>475360</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6580060</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112795528</v>
+      </c>
+      <c r="B27" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>475386</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6580053</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>rönnved</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112795542</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bråten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>475286</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6579916</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-09-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 64125-2021 artfynd.xlsx
+++ b/artfynd/A 64125-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795483</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795506</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795471</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795474</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795475</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795536</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795537</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1919,6 +1979,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795488</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795476</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2126,6 +2196,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795478</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795491</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795523</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2434,6 +2519,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795458</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2540,6 +2630,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795459</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2646,6 +2741,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795469</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795481</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795513</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2949,6 +3059,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795514</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3050,6 +3165,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795516</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3156,6 +3276,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795497</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795527</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3368,6 +3498,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795528</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3469,8 +3604,42 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112795542</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>